--- a/2018/South3/South3_members_final.xlsx
+++ b/2018/South3/South3_members_final.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب سبعة</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب سبعة</t>
         </is>
       </c>
     </row>
